--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.14039232872536</v>
+      </c>
+      <c r="C2">
         <v>26.66272877109077</v>
-      </c>
-      <c r="C2">
-        <v>28.14039232872536</v>
       </c>
       <c r="D2">
         <v>3.750553848352748</v>
       </c>
       <c r="E2">
-        <v>17.22363772878894</v>
+        <v>18.17818150486811</v>
       </c>
       <c r="F2">
         <v>64.59818076634294</v>
       </c>
       <c r="G2">
-        <v>18.17818150486811</v>
+        <v>17.22363772878894</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.94267515923567</v>
+      </c>
+      <c r="C3">
         <v>34.90445859872612</v>
-      </c>
-      <c r="C3">
-        <v>31.94267515923567</v>
       </c>
       <c r="D3">
         <v>2.864963503649635</v>
       </c>
       <c r="E3">
-        <v>20.92002290513457</v>
+        <v>19.14487497614048</v>
       </c>
       <c r="F3">
         <v>59.93510211872495</v>
       </c>
       <c r="G3">
-        <v>19.14487497614048</v>
+        <v>20.92002290513457</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.6510067114094</v>
+      </c>
+      <c r="C4">
         <v>30.84563758389261</v>
-      </c>
-      <c r="C4">
-        <v>31.6510067114094</v>
       </c>
       <c r="D4">
         <v>3.241949521322889</v>
       </c>
       <c r="E4">
-        <v>18.98232281513299</v>
+        <v>19.47794482075004</v>
       </c>
       <c r="F4">
         <v>61.53973236411696</v>
       </c>
       <c r="G4">
-        <v>19.47794482075004</v>
+        <v>18.98232281513299</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.91071428571428</v>
+      </c>
+      <c r="C5">
         <v>29.44915254237288</v>
-      </c>
-      <c r="C5">
-        <v>29.91071428571428</v>
       </c>
       <c r="D5">
         <v>3.39568345323741</v>
       </c>
       <c r="E5">
-        <v>18.47965433740088</v>
+        <v>18.76928920754001</v>
       </c>
       <c r="F5">
         <v>62.75105645505912</v>
       </c>
       <c r="G5">
-        <v>18.76928920754001</v>
+        <v>18.47965433740088</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.65474722564735</v>
+      </c>
+      <c r="C6">
         <v>31.29880805589807</v>
-      </c>
-      <c r="C6">
-        <v>29.65474722564735</v>
       </c>
       <c r="D6">
         <v>3.195009848982272</v>
       </c>
       <c r="E6">
-        <v>19.44586312563841</v>
+        <v>18.4244126659857</v>
       </c>
       <c r="F6">
         <v>62.12972420837589</v>
       </c>
       <c r="G6">
-        <v>18.4244126659857</v>
+        <v>19.44586312563841</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>35.79190235189044</v>
+      </c>
+      <c r="C7">
         <v>28.04406073236082</v>
-      </c>
-      <c r="C7">
-        <v>35.79190235189044</v>
       </c>
       <c r="D7">
         <v>3.565817409766455</v>
       </c>
       <c r="E7">
-        <v>17.11715804297461</v>
+        <v>21.84618180166266</v>
       </c>
       <c r="F7">
         <v>61.03666015536274</v>
       </c>
       <c r="G7">
-        <v>21.84618180166266</v>
+        <v>17.11715804297461</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>31.85785045994182</v>
+      </c>
+      <c r="C8">
         <v>32.58904001886941</v>
-      </c>
-      <c r="C8">
-        <v>31.85785045994182</v>
       </c>
       <c r="D8">
         <v>3.068516284680338</v>
       </c>
       <c r="E8">
-        <v>19.81736469688277</v>
+        <v>19.37272901128323</v>
       </c>
       <c r="F8">
         <v>60.80990629183401</v>
       </c>
       <c r="G8">
-        <v>19.37272901128323</v>
+        <v>19.81736469688277</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.53541575010998</v>
+      </c>
+      <c r="C9">
         <v>29.29168499780027</v>
-      </c>
-      <c r="C9">
-        <v>31.53541575010998</v>
       </c>
       <c r="D9">
         <v>3.413938119555422</v>
       </c>
       <c r="E9">
-        <v>18.21315242367874</v>
+        <v>19.60827223985118</v>
       </c>
       <c r="F9">
         <v>62.17857533647007</v>
       </c>
       <c r="G9">
-        <v>19.60827223985118</v>
+        <v>18.21315242367874</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.82298795373594</v>
+      </c>
+      <c r="C10">
         <v>31.74050506263257</v>
-      </c>
-      <c r="C10">
-        <v>28.82298795373594</v>
       </c>
       <c r="D10">
         <v>3.150548480645568</v>
       </c>
       <c r="E10">
-        <v>19.76819541375873</v>
+        <v>17.95114656031904</v>
       </c>
       <c r="F10">
         <v>62.28065802592224</v>
       </c>
       <c r="G10">
-        <v>17.95114656031904</v>
+        <v>19.76819541375873</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.44539527302364</v>
+      </c>
+      <c r="C11">
         <v>27.39405052974735</v>
-      </c>
-      <c r="C11">
-        <v>33.44539527302364</v>
       </c>
       <c r="D11">
         <v>3.65042766827817</v>
       </c>
       <c r="E11">
-        <v>17.03192297947809</v>
+        <v>20.79427413225235</v>
       </c>
       <c r="F11">
         <v>62.17380288826958</v>
       </c>
       <c r="G11">
-        <v>20.79427413225235</v>
+        <v>17.03192297947809</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>31.98602794411178</v>
+      </c>
+      <c r="C12">
         <v>34.59747172322022</v>
-      </c>
-      <c r="C12">
-        <v>31.98602794411178</v>
       </c>
       <c r="D12">
         <v>2.890384615384615</v>
       </c>
       <c r="E12">
-        <v>20.76884672990514</v>
+        <v>19.20119820269596</v>
       </c>
       <c r="F12">
         <v>60.0299550673989</v>
       </c>
       <c r="G12">
-        <v>19.20119820269596</v>
+        <v>20.76884672990514</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.82737052789592</v>
+      </c>
+      <c r="C13">
         <v>34.39079309482111</v>
-      </c>
-      <c r="C13">
-        <v>29.82737052789592</v>
       </c>
       <c r="D13">
         <v>2.90775498326786</v>
       </c>
       <c r="E13">
-        <v>20.94213717663548</v>
+        <v>18.16325908772357</v>
       </c>
       <c r="F13">
         <v>60.89460373564093</v>
       </c>
       <c r="G13">
-        <v>18.16325908772357</v>
+        <v>20.94213717663548</v>
       </c>
     </row>
   </sheetData>
